--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120711070</v>
+        <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>92098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,37 +827,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trångbodarna, Jmt</t>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501583</v>
+        <v>501920</v>
       </c>
       <c r="R3" t="n">
-        <v>7037272</v>
+        <v>7037319</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +881,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,53 +897,58 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120711070</t>
+          <t>https://artportalen.se/Sighting/136651561</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121213493</v>
+        <v>120711070</v>
       </c>
       <c r="B4" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,22 +988,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,54 +1029,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121213493</t>
+          <t>https://artportalen.se/Sighting/120711070</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121101152</v>
+        <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92632</v>
+        <v>92102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trångbodarna, Jmt</t>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501583</v>
+        <v>501916</v>
       </c>
       <c r="R5" t="n">
-        <v>7037272</v>
+        <v>7037322</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,22 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,69 +1116,74 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121101152</t>
+          <t>https://artportalen.se/Sighting/136651569</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119480526</v>
+        <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>92102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trångbodarna, Jmt</t>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501583</v>
+        <v>501758</v>
       </c>
       <c r="R6" t="n">
-        <v>7037272</v>
+        <v>7037289</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,22 +1207,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,31 +1223,36 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal gransumpskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119480526</t>
+          <t>https://artportalen.se/Sighting/136651573</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129727154</v>
+        <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>92102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,37 +1260,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grötomsbodarna, Jmt</t>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501428</v>
+        <v>501586</v>
       </c>
       <c r="R7" t="n">
-        <v>7037099</v>
+        <v>7036990</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,17 +1314,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spår av födosök, barkflagor</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,92 +1331,73 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Persson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Persson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129727154</t>
+          <t>https://artportalen.se/Sighting/136651580</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129722015</v>
+        <v>121213493</v>
       </c>
       <c r="B8" t="n">
-        <v>58592</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102125</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Häståken, Häståken, Jmt</t>
+          <t>Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501667</v>
+        <v>501583</v>
       </c>
       <c r="R8" t="n">
-        <v>7037322</v>
+        <v>7037272</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,12 +1421,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,59 +1462,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129722015</t>
+          <t>https://artportalen.se/Sighting/121213493</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119483293</v>
+        <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>57144</v>
+        <v>92534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äggskal</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trångbodarna, Jmt</t>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501583</v>
+        <v>501918</v>
       </c>
       <c r="R9" t="n">
-        <v>7037272</v>
+        <v>7037317</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,57 +1533,52 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483293</t>
+          <t>https://artportalen.se/Sighting/136651564</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120381974</v>
+        <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>58114</v>
+        <v>92534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,46 +1586,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Trångbodarna, Jmt</t>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501583</v>
+        <v>501575</v>
       </c>
       <c r="R10" t="n">
-        <v>7037272</v>
+        <v>7036992</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,22 +1640,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,31 +1656,36 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120381974</t>
+          <t>https://artportalen.se/Sighting/136651575</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104839580</v>
+        <v>136651577</v>
       </c>
       <c r="B11" t="n">
-        <v>58057</v>
+        <v>83341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,42 +1693,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trångbodarna, Jmt</t>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501583</v>
+        <v>501496</v>
       </c>
       <c r="R11" t="n">
-        <v>7037272</v>
+        <v>7037090</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,22 +1747,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-11-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-11-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,78 +1763,74 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Eriksson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104839580</t>
+          <t>https://artportalen.se/Sighting/136651577</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129721919</v>
+        <v>121101152</v>
       </c>
       <c r="B12" t="n">
-        <v>58057</v>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Trångbodarna, Trångbodarna, Jmt</t>
+          <t>Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501667</v>
+        <v>501583</v>
       </c>
       <c r="R12" t="n">
-        <v>7037322</v>
+        <v>7037272</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1926,12 +1854,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,7 +1895,1567 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/121101152</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136651568</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>501623</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7037092</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651568</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136651570</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92498</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>501669</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7037107</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651570</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136651563</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93039</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4740</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sotriska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lactarius lignyotus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>501891</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7037311</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651563</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136651562</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92065</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>501670</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7037274</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651562</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119480526</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>501583</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7037272</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480526</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136651579</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>501558</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7036983</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Ört-och mossrik, bördig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651579</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129727154</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Grötomsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>501428</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7037099</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spår av födosök, barkflagor</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129727154</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129722015</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58592</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Häståken, Häståken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>501667</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7037322</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129722015</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>119483293</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äggskal</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>501583</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7037272</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483293</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120381974</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>501583</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7037272</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120381974</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104839580</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>501583</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7037272</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-11-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-11-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104839580</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129721919</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Trångbodarna, Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>501667</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7037322</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129721919</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136651572</v>
+      </c>
+      <c r="B25" t="n">
+        <v>83461</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>501839</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7037362</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal och bördig gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651572</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136651571</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79730</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>501839</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7037362</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gammal och bördig gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651571</t>
         </is>
       </c>
     </row>
@@ -1974,6 +3472,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92327</v>
+        <v>92330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92498</v>
+        <v>92501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93039</v>
+        <v>93042</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92330</v>
+        <v>92331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92501</v>
+        <v>92502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93042</v>
+        <v>93043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136651577</v>
       </c>
       <c r="B11" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92331</v>
+        <v>92336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92502</v>
+        <v>92507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93043</v>
+        <v>93048</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>136651579</v>
       </c>
       <c r="B18" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136651572</v>
       </c>
       <c r="B25" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>136651571</v>
       </c>
       <c r="B26" t="n">
-        <v>79730</v>
+        <v>79732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92336</v>
+        <v>92338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92507</v>
+        <v>92509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93048</v>
+        <v>93050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136651577</v>
       </c>
       <c r="B11" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92509</v>
+        <v>92511</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93050</v>
+        <v>93052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>136651579</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136651572</v>
       </c>
       <c r="B25" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>136651571</v>
       </c>
       <c r="B26" t="n">
-        <v>79732</v>
+        <v>79736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136651577</v>
       </c>
       <c r="B11" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92340</v>
+        <v>92342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92511</v>
+        <v>92513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93052</v>
+        <v>93054</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>136651579</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136651572</v>
       </c>
       <c r="B25" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>136651571</v>
       </c>
       <c r="B26" t="n">
-        <v>79736</v>
+        <v>79738</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136651577</v>
       </c>
       <c r="B11" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92342</v>
+        <v>92343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92513</v>
+        <v>92514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93054</v>
+        <v>93055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>136651579</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136651572</v>
       </c>
       <c r="B25" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>136651571</v>
       </c>
       <c r="B26" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92343</v>
+        <v>92349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92514</v>
+        <v>92520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93055</v>
+        <v>93061</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136651577</v>
       </c>
       <c r="B11" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92349</v>
+        <v>92353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93061</v>
+        <v>93065</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>136651579</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136651572</v>
       </c>
       <c r="B25" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>136651571</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136651577</v>
       </c>
       <c r="B11" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92353</v>
+        <v>92355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93065</v>
+        <v>93067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>136651579</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136651572</v>
       </c>
       <c r="B25" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>136651571</v>
       </c>
       <c r="B26" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136651577</v>
       </c>
       <c r="B11" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92355</v>
+        <v>92368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>92539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93067</v>
+        <v>93080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>136651579</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136651572</v>
       </c>
       <c r="B25" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>136651571</v>
       </c>
       <c r="B26" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38335-2023 artfynd.xlsx
+++ b/artfynd/A 38335-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136651561</v>
       </c>
       <c r="B3" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136651569</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>136651573</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136651580</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>136651564</v>
       </c>
       <c r="B9" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136651575</v>
       </c>
       <c r="B10" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136651577</v>
       </c>
       <c r="B11" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>136651568</v>
       </c>
       <c r="B13" t="n">
-        <v>92368</v>
+        <v>92370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>136651570</v>
       </c>
       <c r="B14" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136651563</v>
       </c>
       <c r="B15" t="n">
-        <v>93080</v>
+        <v>93082</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136651562</v>
       </c>
       <c r="B16" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>136651579</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>136651572</v>
       </c>
       <c r="B25" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>136651571</v>
       </c>
       <c r="B26" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
